--- a/templates/Reit_Prev_FIE - template.xlsx
+++ b/templates/Reit_Prev_FIE - template.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="22.28515625" customWidth="1" style="56" min="1" max="1"/>
@@ -747,8 +747,8 @@
     <col width="5.42578125" customWidth="1" style="56" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="56" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="56" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="56" min="10" max="17"/>
-    <col width="9.140625" customWidth="1" style="56" min="18" max="16384"/>
+    <col width="9.140625" customWidth="1" style="56" min="10" max="18"/>
+    <col width="9.140625" customWidth="1" style="56" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -892,20 +892,20 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1.6344938</v>
+        <v>1.6539029</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>5.322777185234884e-06</v>
+        <v>-0.0006168864089088899</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.009808635311664111</v>
+        <v>-1.136777588679469</v>
       </c>
       <c r="G17" s="4" t="n"/>
     </row>
@@ -913,20 +913,20 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1.6344851</v>
+        <v>1.6549238</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.005292951002392909</v>
+        <v>0.000969140000901092</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>9.753672622065254</v>
+        <v>1.785898696108047</v>
       </c>
       <c r="G18" s="4" t="n"/>
     </row>
@@ -934,20 +934,20 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1.6258794</v>
+        <v>1.6533215</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>-0.00101386795139502</v>
+        <v>0.001460345581402178</v>
       </c>
       <c r="E19" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>-1.868321863444469</v>
+        <v>2.691075868572539</v>
       </c>
       <c r="G19" s="4" t="n"/>
     </row>
@@ -955,20 +955,20 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>1.6275295</v>
+        <v>1.6509106</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>-0.004091381572212227</v>
+        <v>-0.0005983416661672347</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>-7.539460767588336</v>
+        <v>-1.102603958604158</v>
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
@@ -976,20 +976,20 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1.6342157</v>
+        <v>1.651899</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.0005280548016191045</v>
+        <v>0.001495605669369349</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0.973081681499387</v>
+        <v>2.756051976324438</v>
       </c>
       <c r="G21" s="4" t="n"/>
     </row>
@@ -1030,18 +1030,18 @@
     <row r="24" ht="15.95" customHeight="1">
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="44" t="inlineStr"/>
       <c r="D24" s="11" t="n">
-        <v>0.00260432752536266</v>
+        <v>0.005927107483235661</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.2484247102741905</v>
+        <v>1.557786637132555</v>
       </c>
       <c r="G24" s="20" t="n"/>
     </row>
@@ -1054,13 +1054,13 @@
       </c>
       <c r="C25" s="45" t="inlineStr"/>
       <c r="D25" s="15" t="n">
-        <v>0.0056818007020909</v>
+        <v>0.01193399649289839</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>0.4899009921581804</v>
+        <v>1.03679931968348</v>
       </c>
       <c r="G25" s="23" t="n"/>
       <c r="H25" s="24" t="n"/>
@@ -1074,13 +1074,13 @@
       </c>
       <c r="C26" s="45" t="inlineStr"/>
       <c r="D26" s="15" t="n">
-        <v>0.03516653609606779</v>
+        <v>0.04015995253472737</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>0.9965540355590901</v>
+        <v>1.140951307862833</v>
       </c>
       <c r="G26" s="23" t="n"/>
     </row>
@@ -1093,13 +1093,13 @@
       </c>
       <c r="C27" s="45" t="inlineStr"/>
       <c r="D27" s="15" t="n">
-        <v>0.08473811157030053</v>
+        <v>0.09553188181630246</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>1.179082308330164</v>
+        <v>1.330987191762635</v>
       </c>
       <c r="G27" s="23" t="n"/>
     </row>
@@ -1112,13 +1112,13 @@
       </c>
       <c r="C28" s="45" t="inlineStr"/>
       <c r="D28" s="15" t="n">
-        <v>0.1851982856217609</v>
+        <v>0.1946340734407936</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.252889422782649</v>
+        <v>1.314952611589641</v>
       </c>
       <c r="G28" s="23" t="n"/>
     </row>
@@ -1126,18 +1126,18 @@
       <c r="A29" s="25" t="n"/>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr"/>
-      <c r="D29" s="26" t="n">
-        <v>0.03063218190042871</v>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>0.03243902489712824</v>
+      <c r="D29" s="15" t="n">
+        <v>0.2787868811340337</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.2779304689804314</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>0.9443003295435219</v>
+        <v>1.003081389948875</v>
       </c>
       <c r="G29" s="23" t="n"/>
     </row>
@@ -1145,18 +1145,18 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr"/>
       <c r="D30" s="26" t="n">
-        <v>0.1980829630670475</v>
+        <v>0.04287061503594969</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>1.383910820329237</v>
+        <v>1.126532180781164</v>
       </c>
       <c r="G30" s="23" t="n"/>
     </row>
@@ -1164,180 +1164,199 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr"/>
       <c r="D31" s="26" t="n">
-        <v>0.05886832050626944</v>
+        <v>0.1980829630670475</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>0.5390628649056639</v>
-      </c>
-      <c r="G31" s="4" t="n"/>
+        <v>1.383910820329237</v>
+      </c>
+      <c r="G31" s="23" t="n"/>
     </row>
     <row r="32" ht="15.95" customHeight="1">
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr"/>
       <c r="D32" s="26" t="n">
-        <v>0.6344938</v>
+        <v>0.05886832050626944</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0.5892667361628623</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.076751428617273</v>
+        <v>0.5390628649056639</v>
       </c>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34" ht="26.1" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="42" t="inlineStr">
+    <row r="33" ht="15.95" customHeight="1">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr"/>
+      <c r="D33" s="26" t="n">
+        <v>0.6539029000000001</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>0.5979121795447551</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>1.093643719547369</v>
+      </c>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="28" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="46" t="n">
-        <v>42727166.53</v>
-      </c>
-      <c r="F35" s="46" t="n"/>
+      <c r="C35" s="42" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="27" t="n"/>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="29" t="n"/>
       <c r="E36" s="46" t="n">
-        <v>20647809.05662698</v>
+        <v>49088072.35</v>
       </c>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="27" t="n"/>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="46" t="n">
+        <v>21605883.15722222</v>
+      </c>
+      <c r="F37" s="46" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="35" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="37" t="n"/>
-      <c r="C40" s="38" t="n"/>
       <c r="D40" s="36" t="n"/>
       <c r="E40" s="36" t="n"/>
       <c r="F40" s="36" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="51" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="55" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="51" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="57" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="39" t="n"/>
-      <c r="C43" s="39" t="n"/>
-      <c r="D43" s="39" t="n"/>
-      <c r="E43" s="39" t="n"/>
-      <c r="F43" s="39" t="n"/>
+      <c r="B43" s="57" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="40" t="n"/>
-      <c r="C44" s="41" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="23" t="n"/>
+      <c r="B44" s="39" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="40" t="n"/>
       <c r="C45" s="41" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="23" t="n"/>
       <c r="F45" s="23" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="40" t="n"/>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="84"/>
 </worksheet>
 </file>